--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-uiux-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-uiux-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Visual Hierarchy và Progressive Disclosure giúp quản lý tải nhận thức. Bằng cách chỉ hiển thị thông tin quan trọng nhất ở cấp độ cao, và cho phép người dùng đi sâu vào chi tiết theo nhu cầu (drill-down), Dashboard sẽ sạch sẽ và hiệu quả hơn.</v>
       </c>
       <c r="F2" t="str">
-        <v>Áp dụng nguyên tắc "progressive disclosure" (tiết lộ thông tin tăng dần): Chỉ hiển thị các chỉ số tổng quan (KPI cards) ở trên cùng; các bảng dữ liệu chi tiết được ẩn trong các tab hoặc cung cấp tính năng drill-down khi bấm vào — tiết lộ thông tin tăng dần</v>
+        <v>Sử dụng 10 tông màu sắc tương phản mạnh khác nhau để tô nền cho từng khối biểu đồ nhằm tạo sự nổi bật tối đa — đa dạng màu sắc gây nhiễu</v>
       </c>
       <c r="G2" t="str">
         <v>Hiển thị tất cả 15 biểu đồ và 5 bảng số liệu chi tiết kích thước bằng nhau trên cùng một màn hình để người dùng có cái nhìn toàn cảnh ngay lập tức — hiển thị đồng bộ bề mặt</v>
       </c>
       <c r="H2" t="str">
-        <v>Sử dụng 10 tông màu sắc tương phản mạnh khác nhau để tô nền cho từng khối biểu đồ nhằm tạo sự nổi bật tối đa — đa dạng màu sắc gây nhiễu</v>
+        <v>Áp dụng nguyên tắc "progressive disclosure" (tiết lộ thông tin tăng dần): Chỉ hiển thị các chỉ số tổng quan (KPI cards) ở trên cùng; các bảng dữ liệu chi tiết được ẩn trong các tab hoặc cung cấp tính năng drill-down khi bấm vào — tiết lộ thông tin tăng dần</v>
       </c>
       <c r="I2" t="str">
         <v>Tự động ẩn toàn bộ các biểu đồ và chỉ hiển thị số liệu dưới dạng file text thô cho nhẹ trang web — tối giản hóa cực đoan</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Mọi tương tác của người dùng cần có phản hồi lập tức để họ biết hệ thống đã ghi nhận hành động. Thiếu phản hồi trong giao dịch tài chính sẽ gây hoang mang, khiến họ bấm nút chuyển tiền nhiều lần gây trùng lặp giao dịch.</v>
       </c>
       <c r="F3" t="str">
-        <v>Hiển thị màn hình trạng thái đang xử lý (Loading screen kèm thông điệp rõ ràng), tiếp theo là màn hình xác nhận kết quả (Thành công/Thất bại có mã giao dịch) kèm âm thanh phản hồi nhẹ và rung phản hồi (haptic) trên điện thoại — phản hồi đa giác quan hệ thống</v>
+        <v>Gửi một email thông báo kết quả sau 24 giờ và yêu cầu người dùng kiểm tra hòm thư rác để nhận thông tin — phản hồi trễ qua email</v>
       </c>
       <c r="G3" t="str">
         <v>Tự động quay về trang chủ ngay lập tức mà không hiển thị thông báo gì, để người dùng tự kiểm tra lại số dư tài khoản xem đã bị trừ tiền chưa — quay về trang chủ âm thầm</v>
       </c>
       <c r="H3" t="str">
+        <v>Hiển thị màn hình trạng thái đang xử lý (Loading screen kèm thông điệp rõ ràng), tiếp theo là màn hình xác nhận kết quả (Thành công/Thất bại có mã giao dịch) kèm âm thanh phản hồi nhẹ và rung phản hồi (haptic) trên điện thoại — phản hồi đa giác quan hệ thống</v>
+      </c>
+      <c r="I3" t="str">
         <v>Hiển thị một popup bắt buộc người dùng phải nhập lại mã OTP một lần nữa để xác nhận họ thực sự muốn chuyển khoản — xác thực lặp thừa</v>
       </c>
-      <c r="I3" t="str">
-        <v>Gửi một email thông báo kết quả sau 24 giờ và yêu cầu người dùng kiểm tra hòm thư rác để nhận thông tin — phản hồi trễ qua email</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Empty States là cơ hội tuyệt vời để tương tác với người dùng. Thay vì dẫn họ vào ngõ cụt (Dead-end), một thiết kế thông minh sẽ khơi gợi nhu cầu và dẫn dắt họ tiếp tục trải nghiệm sản phẩm bằng các nút gợi ý hành động.</v>
       </c>
       <c r="F4" t="str">
+        <v>Để hiển thị bảng danh sách các lập trình viên đã viết ra trang web đó nhằm tăng độ tin cậy thương hiệu — hiển thị danh sách dev</v>
+      </c>
+      <c r="G4" t="str">
         <v>Vì thay vì chỉ hiển thị một trang trắng trơn gây cảm giác cụt luồng, Empty State tốt sẽ giải thích bối cảnh, kết hợp hình ảnh minh họa thân thiện và đưa ra nút CTA hành động tiếp theo (ví dụ: "Mua sắm ngay", "Thử từ khóa khác") — định hướng hành vi tiếp theo</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Để hệ thống tự động tải ngẫu nhiên các sản phẩm giá cao nhất và tự động chèn vào giỏ hàng của khách hàng — tự động chèn đơn hàng</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Để hiển thị bảng danh sách các lập trình viên đã viết ra trang web đó nhằm tăng độ tin cậy thương hiệu — hiển thị danh sách dev</v>
       </c>
       <c r="I4" t="str">
         <v>Để bắt buộc người dùng phải đăng xuất tài khoản và đăng nhập lại bằng một tài khoản khác có nhiều dữ liệu hơn — ép đăng xuất</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Accessibility (A11y) là tiêu chuẩn bắt buộc đối với các phần mềm doanh nghiệp hoặc dịch vụ công. BA phải thiết kế các thành phần UI có độ tương phản đạt chuẩn WCAG (thường tối thiểu 4.5:1), hỗ trợ điều hướng hoàn toàn bằng bàn phím (tab index) cho người không dùng được chuột.</v>
       </c>
       <c r="F5" t="str">
+        <v>Để ngăn chặn các cuộc tấn công đánh cắp dữ liệu từ các thiết bị ngoại vi kết nối vào máy chủ — bảo mật thiết bị ngoại vi</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Để phần mềm chạy mượt mà trên các dòng điện thoại di động giá rẻ có cấu hình RAM dưới 1GB — tối ưu hóa phần cứng di động</v>
+      </c>
+      <c r="H5" t="str">
         <v>Để đảm bảo nhân viên bị hạn chế về khả năng (như mù màu, thị lực kém) vẫn có thể vận hành hệ thống thông qua việc tối ưu độ tương phản màu sắc (contrast ratio), hỗ trợ phím tắt và đọc được bằng Screen Reader — hỗ trợ tiếp cận hòa nhập</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Để hệ thống tự động dịch giao diện sang 100 ngôn ngữ khác nhau trên thế giới bằng thuật toán dịch máy Google Translate — dịch thuật giao diện</v>
       </c>
-      <c r="H5" t="str">
-        <v>Để phần mềm chạy mượt mà trên các dòng điện thoại di động giá rẻ có cấu hình RAM dưới 1GB — tối ưu hóa phần cứng di động</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Để ngăn chặn các cuộc tấn công đánh cắp dữ liệu từ các thiết bị ngoại vi kết nối vào máy chủ — bảo mật thiết bị ngoại vi</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Cognitive Tunneling là hiện tượng tâm lý khi bị stress hoặc quá tập trung, tầm nhìn của con người bị thu hẹp. Nếu thiết kế nút "Hủy đơn" và cảnh báo mất tiền ở góc xa, họ sẽ không thấy. BA phải đưa thông tin quan trọng vào tiêu điểm thị giác trực tiếp (visual anchor).</v>
       </c>
       <c r="F6" t="str">
+        <v>Người dùng liên tục bấm phím F5 để tải lại trang web do tốc độ load quá chậm; BA cần tối ưu hóa các câu lệnh truy vấn SQL ở database — tối ưu hóa cơ sở dữ liệu</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Người dùng từ chối tham gia bài test vì giao diện thiết kế quá xấu và thiếu màu sắc; BA cần thuê designer vẽ lại đồ họa 3D đẹp mắt — thiết kế đồ họa lại</v>
+      </c>
+      <c r="H6" t="str">
         <v>Người dùng quá tập trung vào một khu vực màn hình hoặc một luồng thao tác quen thuộc dẫn đến việc bỏ sót các thông tin cảnh báo quan trọng ở góc khác; BA cần điều chỉnh bằng cách đưa cảnh báo vào giữa tiêu điểm thị giác hoặc dùng popup modal chặn luồng khi có sự cố nghiêm trọng — điều chỉnh tiêu điểm nhận thức</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Người dùng liên tục bấm phím F5 để tải lại trang web do tốc độ load quá chậm; BA cần tối ưu hóa các câu lệnh truy vấn SQL ở database — tối ưu hóa cơ sở dữ liệu</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Người dùng từ chối tham gia bài test vì giao diện thiết kế quá xấu và thiếu màu sắc; BA cần thuê designer vẽ lại đồ họa 3D đẹp mắt — thiết kế đồ họa lại</v>
       </c>
       <c r="I6" t="str">
         <v>Người dùng tự động viết code để vượt qua các bước bảo mật của bản mẫu; BA cần cài đặt thêm phần mềm diệt virus trên máy tính test — diệt virus máy tính</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Thumb Zone chỉ ra các vùng trên màn hình di động dễ chạm (Easy), cần với (Stretch) và khó chạm (Ow) khi dùng 1 tay. Thiết kế tốt sẽ đặt các tương tác thường xuyên (như Menu, CTA mua hàng) vào vùng Easy (cạnh dưới màn hình), và các nút nguy hiểm như Xóa tài khoản vào vùng Ow (cạnh trên).</v>
       </c>
       <c r="F7" t="str">
+        <v>Để ngăn chặn người dùng vô tình chạm các ngón tay khác vào màn hình làm loạn cảm ứng — ngăn chạm nhầm</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Vì hệ điều hành iOS và Android bắt buộc tất cả các ứng dụng di động phải đặt nút bấm ở cạnh dưới — quy định hệ điều hành</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Vì ngón tay cái có diện tích tiếp xúc lớn nhất nên cần thiết kế các nút bấm ở cạnh trên màn hình có kích thước nhỏ lại — kích thước nút cạnh trên</v>
+      </c>
+      <c r="I7" t="str">
         <v>Vì ngón tay cái là ngón tay tương tác chủ yếu khi sử dụng điện thoại bằng một tay; các khu vực ở cạnh dưới và giữa màn hình là vùng dễ chạm tới nhất mà không gây mỏi tay — tối ưu hóa vùng chạm một tay</v>
       </c>
-      <c r="G7" t="str">
-        <v>Vì ngón tay cái có diện tích tiếp xúc lớn nhất nên cần thiết kế các nút bấm ở cạnh trên màn hình có kích thước nhỏ lại — kích thước nút cạnh trên</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Để ngăn chặn người dùng vô tình chạm các ngón tay khác vào màn hình làm loạn cảm ứng — ngăn chạm nhầm</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Vì hệ điều hành iOS và Android bắt buộc tất cả các ứng dụng di động phải đặt nút bấm ở cạnh dưới — quy định hệ điều hành</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Đây là tư duy thiết kế luồng đi linh hoạt (Progressive Profiling). Việc bắt buộc eKYC ngay từ đầu tạo ra rào cản rất lớn (Friction). Trì hoãn việc yêu cầu thông tin nhạy cảm cho đến khi nó thực sự cần thiết (Just-in-time) giúp tăng tỷ lệ chuyển đổi người dùng đăng ký ban đầu.</v>
       </c>
       <c r="F8" t="str">
+        <v>Yêu cầu người dùng phải đến trực tiếp văn phòng chi nhánh để ký giấy tờ trước rồi mới cho phép tải ứng dụng — quy trình thuần truyền thống</v>
+      </c>
+      <c r="G8" t="str">
         <v>Thiết kế luồng eKYC phân cấp: Cho phép người dùng đăng ký tài khoản nhanh bằng số điện thoại để trải nghiệm xem bảng giá trước (MVP); chỉ yêu cầu xác thực eKYC đầy đủ khi họ thực hiện nạp tiền hoặc giao dịch mua bán thực tế — trì hoãn xác thực tăng chuyển đổi</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Bắt buộc người dùng phải hoàn thành toàn bộ 10 bước xác thực bảo mật khắt khe ngay khi vừa mở ứng dụng lần đầu tiên thì mới cho xem thông tin — xác thực khắt khe chặn người dùng</v>
       </c>
       <c r="H8" t="str">
         <v>Loại bỏ hoàn toàn bước chụp ảnh căn cước công dân và ký số để người dùng đăng ký nhanh nhất có thể — vi phạm quy định pháp lý an toàn</v>
       </c>
       <c r="I8" t="str">
-        <v>Yêu cầu người dùng phải đến trực tiếp văn phòng chi nhánh để ký giấy tờ trước rồi mới cho phép tải ứng dụng — quy trình thuần truyền thống</v>
+        <v>Bắt buộc người dùng phải hoàn thành toàn bộ 10 bước xác thực bảo mật khắt khe ngay khi vừa mở ứng dụng lần đầu tiên thì mới cho xem thông tin — xác thực khắt khe chặn người dùng</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -690,10 +690,10 @@
         <v>Người dùng sẽ đưa ra quyết định nhanh hơn nếu hệ thống cung cấp cho họ tối thiểu 50 lựa chọn khác nhau trên cùng một trang — tăng số lượng lựa chọn</v>
       </c>
       <c r="H9" t="str">
+        <v>Quy định rằng menu của website chỉ được phép hiển thị chữ viết chứ không được phép có icon minh họa kèm theo — menu thô</v>
+      </c>
+      <c r="I9" t="str">
         <v>Hệ thống bắt buộc phải tự động chọn ngẫu nhiên một dịch vụ cho khách hàng nếu họ không bấm chọn sau 5 giây — tự động chọn ngẫu nhiên</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Quy định rằng menu của website chỉ được phép hiển thị chữ viết chứ không được phép có icon minh họa kèm theo — menu thô</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -751,13 +751,13 @@
         <v>Vì nó thiết lập các thành phần giao diện mẫu tái sử dụng được (Reusable Components) giúp Dev chỉ cần code một lần và tái sử dụng, còn QA có bộ quy tắc chuẩn để kiểm thử tính nhất quán — chuẩn hóa thành phần giao diện</v>
       </c>
       <c r="G11" t="str">
-        <v>Vì nó tự động dịch các bản vẽ Wireframe thành mã nguồn React/Angular mà không cần lập trình viên Frontend viết code — tự động sinh code Frontend</v>
+        <v>Vì nó loại bỏ hoàn toàn giai đoạn kiểm thử giao diện người dùng của đội ngũ QA — loại bỏ kiểm thử UI</v>
       </c>
       <c r="H11" t="str">
         <v>Vì nó bắt buộc khách hàng phải tuân thủ giao diện mẫu và không bao giờ được phép yêu cầu thay đổi thiết kế nữa — khóa yêu cầu giao diện</v>
       </c>
       <c r="I11" t="str">
-        <v>Vì nó loại bỏ hoàn toàn giai đoạn kiểm thử giao diện người dùng của đội ngũ QA — loại bỏ kiểm thử UI</v>
+        <v>Vì nó tự động dịch các bản vẽ Wireframe thành mã nguồn React/Angular mà không cần lập trình viên Frontend viết code — tự động sinh code Frontend</v>
       </c>
       <c r="J11">
         <v>1</v>
